--- a/convert/Cong_thang_4.xlsx
+++ b/convert/Cong_thang_4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>2022-04-01</t>
   </si>
@@ -64,7 +64,7 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>P</t>
+    <t>Co don nhung di lam</t>
   </si>
   <si>
     <t>A</t>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>P0</t>
-  </si>
-  <si>
-    <t>L</t>
   </si>
 </sst>
 </file>
@@ -493,7 +490,7 @@
         <v>21</v>
       </c>
       <c r="W8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="s">
         <v>21</v>

--- a/convert/Cong_thang_4.xlsx
+++ b/convert/Cong_thang_4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19418" uniqueCount="1683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19412" uniqueCount="1683">
   <si>
     <t>2022-04-01</t>
   </si>
@@ -6203,10 +6203,7 @@
         <v>4</v>
       </c>
       <c r="AO13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP13">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="AQ13" t="s">
         <v>45</v>
@@ -6237,6 +6234,9 @@
       </c>
       <c r="AZ13">
         <v>4</v>
+      </c>
+      <c r="BB13">
+        <v>16</v>
       </c>
       <c r="BC13" t="s">
         <v>47</v>
@@ -20438,7 +20438,7 @@
         <v>364</v>
       </c>
       <c r="AU109" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AW109" t="s">
         <v>45</v>
@@ -20980,7 +20980,7 @@
         <v>36</v>
       </c>
       <c r="BL113">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BM113" t="s">
         <v>36</v>
@@ -29778,9 +29778,6 @@
       <c r="AL170">
         <v>4</v>
       </c>
-      <c r="AM170" t="s">
-        <v>92</v>
-      </c>
       <c r="AN170">
         <v>12</v>
       </c>
@@ -29816,6 +29813,9 @@
       </c>
       <c r="AZ170">
         <v>4</v>
+      </c>
+      <c r="BB170">
+        <v>8</v>
       </c>
       <c r="BC170" t="s">
         <v>35</v>
@@ -33879,9 +33879,6 @@
       <c r="AZ197">
         <v>4</v>
       </c>
-      <c r="BA197" t="s">
-        <v>92</v>
-      </c>
       <c r="BB197">
         <v>8</v>
       </c>
@@ -41648,7 +41645,7 @@
         <v>4</v>
       </c>
       <c r="L250">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M250" t="s">
         <v>45</v>
@@ -47328,7 +47325,10 @@
         <v>4</v>
       </c>
       <c r="AI288" t="s">
-        <v>35</v>
+        <v>45</v>
+      </c>
+      <c r="AJ288">
+        <v>4</v>
       </c>
       <c r="AK288" t="s">
         <v>45</v>
@@ -47336,6 +47336,9 @@
       <c r="AL288">
         <v>4</v>
       </c>
+      <c r="AN288">
+        <v>12</v>
+      </c>
       <c r="AO288" t="s">
         <v>47</v>
       </c>
@@ -47371,6 +47374,9 @@
       </c>
       <c r="AZ288">
         <v>4</v>
+      </c>
+      <c r="BB288">
+        <v>8</v>
       </c>
       <c r="BC288" t="s">
         <v>45</v>
@@ -56753,6 +56759,9 @@
       <c r="AZ354">
         <v>4</v>
       </c>
+      <c r="BB354">
+        <v>4</v>
+      </c>
       <c r="BC354" t="s">
         <v>45</v>
       </c>
@@ -58111,7 +58120,7 @@
         <v>4</v>
       </c>
       <c r="L365">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M365" t="s">
         <v>45</v>
@@ -61213,6 +61222,9 @@
       <c r="AZ388">
         <v>4</v>
       </c>
+      <c r="BB388">
+        <v>4</v>
+      </c>
       <c r="BC388" t="s">
         <v>45</v>
       </c>
@@ -64200,12 +64212,6 @@
       <c r="AZ407">
         <v>4</v>
       </c>
-      <c r="BA407" t="s">
-        <v>92</v>
-      </c>
-      <c r="BB407">
-        <v>8</v>
-      </c>
       <c r="BC407" t="s">
         <v>45</v>
       </c>
@@ -68632,6 +68638,9 @@
       <c r="AZ436">
         <v>4</v>
       </c>
+      <c r="BB436">
+        <v>8</v>
+      </c>
       <c r="BC436" t="s">
         <v>45</v>
       </c>
@@ -73562,6 +73571,9 @@
       <c r="AZ474">
         <v>4</v>
       </c>
+      <c r="BB474">
+        <v>16</v>
+      </c>
       <c r="BC474" t="s">
         <v>47</v>
       </c>
@@ -77895,6 +77907,9 @@
       <c r="AL509">
         <v>4</v>
       </c>
+      <c r="AN509">
+        <v>16</v>
+      </c>
       <c r="AO509" t="s">
         <v>47</v>
       </c>
@@ -77930,6 +77945,9 @@
       </c>
       <c r="AZ509">
         <v>4</v>
+      </c>
+      <c r="BB509">
+        <v>8</v>
       </c>
       <c r="BC509" t="s">
         <v>45</v>
@@ -79130,22 +79148,25 @@
         <v>4</v>
       </c>
       <c r="BC523" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="BD523">
+        <v>4</v>
       </c>
       <c r="BE523" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="BF523">
         <v>4</v>
       </c>
       <c r="BG523" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="BH523">
         <v>4</v>
       </c>
       <c r="BI523" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="BK523" t="s">
         <v>36</v>
@@ -79286,22 +79307,25 @@
         <v>4</v>
       </c>
       <c r="BC526" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="BD526">
+        <v>4</v>
       </c>
       <c r="BE526" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="BF526">
         <v>4</v>
       </c>
       <c r="BG526" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="BH526">
         <v>4</v>
       </c>
       <c r="BI526" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="BJ526">
         <v>4</v>
@@ -83784,9 +83808,6 @@
       <c r="AL557">
         <v>4</v>
       </c>
-      <c r="AM557" t="s">
-        <v>92</v>
-      </c>
       <c r="AN557">
         <v>14</v>
       </c>
@@ -89991,12 +90012,6 @@
       <c r="W599" t="s">
         <v>36</v>
       </c>
-      <c r="Y599" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z599">
-        <v>5</v>
-      </c>
       <c r="AA599" t="s">
         <v>51</v>
       </c>
@@ -90020,12 +90035,6 @@
       </c>
       <c r="AK599" t="s">
         <v>51</v>
-      </c>
-      <c r="AM599" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN599">
-        <v>2</v>
       </c>
       <c r="AO599" t="s">
         <v>51</v>
@@ -91401,6 +91410,9 @@
       <c r="AZ608">
         <v>4</v>
       </c>
+      <c r="BB608">
+        <v>4</v>
+      </c>
       <c r="BC608" t="s">
         <v>35</v>
       </c>
@@ -93720,6 +93732,9 @@
       <c r="AZ623">
         <v>4</v>
       </c>
+      <c r="BB623">
+        <v>16</v>
+      </c>
       <c r="BC623" t="s">
         <v>47</v>
       </c>
@@ -94012,6 +94027,9 @@
       <c r="AL625">
         <v>4</v>
       </c>
+      <c r="AN625">
+        <v>16</v>
+      </c>
       <c r="AO625" t="s">
         <v>47</v>
       </c>
@@ -94047,6 +94065,9 @@
       </c>
       <c r="AZ625">
         <v>4</v>
+      </c>
+      <c r="BB625">
+        <v>8</v>
       </c>
       <c r="BC625" t="s">
         <v>45</v>

--- a/convert/Cong_thang_4.xlsx
+++ b/convert/Cong_thang_4.xlsx
@@ -45183,7 +45183,7 @@
         <v>51</v>
       </c>
       <c r="AL273">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM273" t="s">
         <v>92</v>
@@ -82280,7 +82280,7 @@
         <v>36</v>
       </c>
       <c r="BL547">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="BM547" t="s">
         <v>36</v>
@@ -92773,7 +92773,7 @@
         <v>92</v>
       </c>
       <c r="Z617">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA617" t="s">
         <v>47</v>

--- a/convert/Cong_thang_4.xlsx
+++ b/convert/Cong_thang_4.xlsx
@@ -11850,7 +11850,10 @@
         <v>12</v>
       </c>
       <c r="AA51" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="AB51">
+        <v>4</v>
       </c>
       <c r="AC51" t="s">
         <v>45</v>
@@ -16379,7 +16382,10 @@
         <v>12</v>
       </c>
       <c r="AO82" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="AP82">
+        <v>4</v>
       </c>
       <c r="AQ82" t="s">
         <v>45</v>
@@ -22340,9 +22346,6 @@
       <c r="J123">
         <v>4</v>
       </c>
-      <c r="L123">
-        <v>4</v>
-      </c>
       <c r="M123" t="s">
         <v>45</v>
       </c>
@@ -22410,9 +22413,6 @@
         <v>47</v>
       </c>
       <c r="AL123">
-        <v>4</v>
-      </c>
-      <c r="AN123">
         <v>4</v>
       </c>
       <c r="AO123" t="s">
@@ -28230,9 +28230,6 @@
       <c r="J161">
         <v>4</v>
       </c>
-      <c r="L161">
-        <v>4</v>
-      </c>
       <c r="M161" t="s">
         <v>35</v>
       </c>
@@ -34615,9 +34612,6 @@
       <c r="J202">
         <v>4</v>
       </c>
-      <c r="L202">
-        <v>4</v>
-      </c>
       <c r="M202" t="s">
         <v>45</v>
       </c>
@@ -34670,9 +34664,6 @@
         <v>47</v>
       </c>
       <c r="AL202">
-        <v>4</v>
-      </c>
-      <c r="AN202">
         <v>4</v>
       </c>
       <c r="AO202" t="s">
@@ -35902,7 +35893,10 @@
         <v>12</v>
       </c>
       <c r="AO212" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="AP212">
+        <v>4</v>
       </c>
       <c r="AQ212" t="s">
         <v>45</v>
@@ -36050,9 +36044,6 @@
       <c r="AL213">
         <v>4</v>
       </c>
-      <c r="AN213">
-        <v>4</v>
-      </c>
       <c r="AO213" t="s">
         <v>45</v>
       </c>
@@ -39071,7 +39062,10 @@
         <v>12</v>
       </c>
       <c r="BC232" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="BD232">
+        <v>4</v>
       </c>
       <c r="BE232" t="s">
         <v>45</v>
@@ -56759,9 +56753,6 @@
       <c r="AZ354">
         <v>4</v>
       </c>
-      <c r="BB354">
-        <v>4</v>
-      </c>
       <c r="BC354" t="s">
         <v>45</v>
       </c>
@@ -61222,9 +61213,6 @@
       <c r="AZ388">
         <v>4</v>
       </c>
-      <c r="BB388">
-        <v>4</v>
-      </c>
       <c r="BC388" t="s">
         <v>45</v>
       </c>
@@ -64924,9 +64912,6 @@
       <c r="AL412">
         <v>4</v>
       </c>
-      <c r="AN412">
-        <v>4</v>
-      </c>
       <c r="AO412" t="s">
         <v>45</v>
       </c>
@@ -69123,9 +69108,6 @@
       <c r="AL440">
         <v>4</v>
       </c>
-      <c r="AN440">
-        <v>4</v>
-      </c>
       <c r="AO440" t="s">
         <v>45</v>
       </c>
@@ -83511,7 +83493,10 @@
         <v>12</v>
       </c>
       <c r="BC555" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="BD555">
+        <v>4</v>
       </c>
       <c r="BE555" t="s">
         <v>45</v>
@@ -91408,9 +91393,6 @@
         <v>47</v>
       </c>
       <c r="AZ608">
-        <v>4</v>
-      </c>
-      <c r="BB608">
         <v>4</v>
       </c>
       <c r="BC608" t="s">
